--- a/Fase 2/Evidencias Grupales/Historias de Usuario_casos de uso_requerimientos.xlsx
+++ b/Fase 2/Evidencias Grupales/Historias de Usuario_casos de uso_requerimientos.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrador\Documents\GitHub\APT-DUOCUC\Fase 2\Evidencias Grupales\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F12F6E8-8ACC-4941-BA8D-98EF222C84D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EDE356E5-C3AA-4F80-ABBD-D63955FE8A22}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" firstSheet="3" activeTab="4" xr2:uid="{04A9C2FD-01B0-4606-AF92-5DF78A3613E5}"/>
+    <workbookView xWindow="11520" yWindow="0" windowWidth="11520" windowHeight="12360" firstSheet="1" activeTab="1" xr2:uid="{04A9C2FD-01B0-4606-AF92-5DF78A3613E5}"/>
   </bookViews>
   <sheets>
     <sheet name="Historias de Usuario" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="360" uniqueCount="252">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="368" uniqueCount="259">
   <si>
     <t>ID</t>
   </si>
@@ -660,9 +660,6 @@
     <t>El backend debe implementar limitación de peticiones (rate limiting) por usuario/IP para evitar abuso del servicio.</t>
   </si>
   <si>
-    <t>Los contenedores deben ejecutarse en redes privadas dentro de Proxmox, exponiendo solo el proxy.</t>
-  </si>
-  <si>
     <t>RNF-02</t>
   </si>
   <si>
@@ -796,13 +793,42 @@
   </si>
   <si>
     <t>El conjunto de requerimientos definidos asegura la consistencia entre los módulos funcionales y la arquitectura propuesta de SmartSwim. La separación de responsabilidades entre el frontend (React Native) y el backend (FastAPI) permite una evolución modular del sistema, mientras que el uso de Ollama (Gemma3:4B) proporciona una IA local eficiente y controlada. Los requerimientos no funcionales garantizan seguridad, escalabilidad y cumplimiento normativo, asegurando la sostenibilidad técnica del sistema a largo plazo.</t>
+  </si>
+  <si>
+    <t>Autenticación Supabase</t>
+  </si>
+  <si>
+    <t>Credenciales válidas de Supabase</t>
+  </si>
+  <si>
+    <t>CU-11</t>
+  </si>
+  <si>
+    <t>Autenticar acceso seguro en la app</t>
+  </si>
+  <si>
+    <t>Usuario autenticado y token JWT válido; datos correctos almacenados localmente.</t>
+  </si>
+  <si>
+    <t>1. Usuario ingresa email y contraseña.
+2. App envía a Supabase Auth.
+3. Supabase retorna JWT y datos usuario.
+4. Token se almacena localmente.
+5. Requests posteriores incluyen JWT.</t>
+  </si>
+  <si>
+    <t>1. Autenticación falla: mensaje error.
+2. Opción recuperar contraseña.</t>
+  </si>
+  <si>
+    <t>Los contenedores deben ejecutarse en redes privadas dentro de Supabase</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -835,19 +861,35 @@
       <family val="2"/>
     </font>
     <font>
+      <sz val="10"/>
+      <color rgb="FF0F1115"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color rgb="FF0F1115"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
       <sz val="9"/>
       <color theme="1"/>
       <name val="Segoe UI"/>
       <family val="2"/>
     </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF0F1115"/>
-      <name val="Segoe UI"/>
-      <family val="2"/>
-    </font>
   </fonts>
-  <fills count="3">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -857,6 +899,18 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFFFF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="3" tint="0.749992370372631"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -888,7 +942,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
@@ -899,12 +953,22 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1" shrinkToFit="1"/>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1243,31 +1307,33 @@
   <dimension ref="A1:F13"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
+    <col min="1" max="1" width="11.5546875" style="9"/>
     <col min="5" max="5" width="11.44140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="21.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="6" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" ht="330" x14ac:dyDescent="0.3">
-      <c r="A2" s="2" t="s">
+    <row r="2" spans="1:6" ht="145.19999999999999" x14ac:dyDescent="0.3">
+      <c r="A2" s="8" t="s">
         <v>6</v>
       </c>
       <c r="B2" s="2" t="s">
@@ -1286,8 +1352,8 @@
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:6" ht="250.8" x14ac:dyDescent="0.3">
-      <c r="A3" s="2" t="s">
+    <row r="3" spans="1:6" ht="118.8" x14ac:dyDescent="0.3">
+      <c r="A3" s="8" t="s">
         <v>12</v>
       </c>
       <c r="B3" s="2" t="s">
@@ -1306,8 +1372,8 @@
         <v>16</v>
       </c>
     </row>
-    <row r="4" spans="1:6" ht="250.8" x14ac:dyDescent="0.3">
-      <c r="A4" s="2" t="s">
+    <row r="4" spans="1:6" ht="105.6" x14ac:dyDescent="0.3">
+      <c r="A4" s="8" t="s">
         <v>17</v>
       </c>
       <c r="B4" s="2" t="s">
@@ -1326,8 +1392,8 @@
         <v>22</v>
       </c>
     </row>
-    <row r="5" spans="1:6" ht="145.19999999999999" x14ac:dyDescent="0.3">
-      <c r="A5" s="2" t="s">
+    <row r="5" spans="1:6" ht="66" x14ac:dyDescent="0.3">
+      <c r="A5" s="8" t="s">
         <v>23</v>
       </c>
       <c r="B5" s="2" t="s">
@@ -1346,8 +1412,8 @@
         <v>26</v>
       </c>
     </row>
-    <row r="6" spans="1:6" ht="356.4" x14ac:dyDescent="0.3">
-      <c r="A6" s="2" t="s">
+    <row r="6" spans="1:6" ht="171.6" x14ac:dyDescent="0.3">
+      <c r="A6" s="8" t="s">
         <v>27</v>
       </c>
       <c r="B6" s="2" t="s">
@@ -1366,8 +1432,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="7" spans="1:6" ht="198" x14ac:dyDescent="0.3">
-      <c r="A7" s="2" t="s">
+    <row r="7" spans="1:6" ht="92.4" x14ac:dyDescent="0.3">
+      <c r="A7" s="8" t="s">
         <v>33</v>
       </c>
       <c r="B7" s="2" t="s">
@@ -1386,8 +1452,8 @@
         <v>36</v>
       </c>
     </row>
-    <row r="8" spans="1:6" ht="224.4" x14ac:dyDescent="0.3">
-      <c r="A8" s="2" t="s">
+    <row r="8" spans="1:6" ht="105.6" x14ac:dyDescent="0.3">
+      <c r="A8" s="8" t="s">
         <v>37</v>
       </c>
       <c r="B8" s="2" t="s">
@@ -1406,8 +1472,8 @@
         <v>41</v>
       </c>
     </row>
-    <row r="9" spans="1:6" ht="158.4" x14ac:dyDescent="0.3">
-      <c r="A9" s="2" t="s">
+    <row r="9" spans="1:6" ht="79.2" x14ac:dyDescent="0.3">
+      <c r="A9" s="8" t="s">
         <v>42</v>
       </c>
       <c r="B9" s="2" t="s">
@@ -1426,8 +1492,8 @@
         <v>45</v>
       </c>
     </row>
-    <row r="10" spans="1:6" ht="224.4" x14ac:dyDescent="0.3">
-      <c r="A10" s="2" t="s">
+    <row r="10" spans="1:6" ht="118.8" x14ac:dyDescent="0.3">
+      <c r="A10" s="8" t="s">
         <v>46</v>
       </c>
       <c r="B10" s="2" t="s">
@@ -1446,8 +1512,8 @@
         <v>50</v>
       </c>
     </row>
-    <row r="11" spans="1:6" ht="198" x14ac:dyDescent="0.3">
-      <c r="A11" s="2" t="s">
+    <row r="11" spans="1:6" ht="105.6" x14ac:dyDescent="0.3">
+      <c r="A11" s="8" t="s">
         <v>51</v>
       </c>
       <c r="B11" s="2" t="s">
@@ -1466,8 +1532,8 @@
         <v>54</v>
       </c>
     </row>
-    <row r="12" spans="1:6" ht="171.6" x14ac:dyDescent="0.3">
-      <c r="A12" s="2" t="s">
+    <row r="12" spans="1:6" ht="79.2" x14ac:dyDescent="0.3">
+      <c r="A12" s="8" t="s">
         <v>55</v>
       </c>
       <c r="B12" s="2" t="s">
@@ -1486,8 +1552,8 @@
         <v>59</v>
       </c>
     </row>
-    <row r="13" spans="1:6" ht="132" x14ac:dyDescent="0.3">
-      <c r="A13" s="2" t="s">
+    <row r="13" spans="1:6" ht="79.2" x14ac:dyDescent="0.3">
+      <c r="A13" s="8" t="s">
         <v>60</v>
       </c>
       <c r="B13" s="2" t="s">
@@ -1513,37 +1579,45 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8140A96F-95AA-4C4F-9105-D076ED2DC5FF}">
-  <dimension ref="A1:H11"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="13.109375" customWidth="1"/>
+    <col min="4" max="4" width="16.77734375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="24.109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="81.6640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="26.109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="18" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="6" t="s">
         <v>64</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="6" t="s">
         <v>65</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="6" t="s">
         <v>66</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="6" t="s">
         <v>67</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="6" t="s">
         <v>68</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="6" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="409.6" x14ac:dyDescent="0.3">
-      <c r="A2" s="2" t="s">
+    <row r="2" spans="1:8" ht="55.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="8" t="s">
         <v>70</v>
       </c>
       <c r="B2" s="2" t="s">
@@ -1568,8 +1642,8 @@
         <v>76</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="237.6" x14ac:dyDescent="0.3">
-      <c r="A3" s="2" t="s">
+    <row r="3" spans="1:8" ht="79.2" x14ac:dyDescent="0.3">
+      <c r="A3" s="8" t="s">
         <v>77</v>
       </c>
       <c r="B3" s="2" t="s">
@@ -1594,34 +1668,34 @@
         <v>82</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="382.8" x14ac:dyDescent="0.3">
-      <c r="A4" s="2" t="s">
+    <row r="4" spans="1:8" ht="66" x14ac:dyDescent="0.3">
+      <c r="A4" s="8" t="s">
         <v>83</v>
       </c>
-      <c r="B4" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="H4" s="2" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" ht="330" x14ac:dyDescent="0.3">
-      <c r="A5" s="2" t="s">
+      <c r="B4" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>252</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" ht="66" x14ac:dyDescent="0.3">
+      <c r="A5" s="8" t="s">
         <v>90</v>
       </c>
       <c r="B5" s="2" t="s">
@@ -1631,101 +1705,101 @@
         <v>84</v>
       </c>
       <c r="D5" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="52.8" x14ac:dyDescent="0.3">
+      <c r="A6" s="8" t="s">
+        <v>96</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="D6" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="E5" s="2" t="s">
+      <c r="E6" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="F5" s="2" t="s">
+      <c r="F6" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="G5" s="2" t="s">
+      <c r="G6" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="H5" s="2" t="s">
+      <c r="H6" s="2" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="6" spans="1:8" ht="409.2" x14ac:dyDescent="0.3">
-      <c r="A6" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="H6" s="2" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" ht="290.39999999999998" x14ac:dyDescent="0.3">
-      <c r="A7" s="2" t="s">
+    <row r="7" spans="1:8" ht="52.8" x14ac:dyDescent="0.3">
+      <c r="A7" s="8" t="s">
         <v>103</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>28</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>84</v>
+        <v>97</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" ht="250.8" x14ac:dyDescent="0.3">
-      <c r="A8" s="2" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" ht="52.8" x14ac:dyDescent="0.3">
+      <c r="A8" s="8" t="s">
         <v>109</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>84</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>110</v>
+        <v>104</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>113</v>
+        <v>107</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" ht="250.8" x14ac:dyDescent="0.3">
-      <c r="A9" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" ht="66" x14ac:dyDescent="0.3">
+      <c r="A9" s="8" t="s">
         <v>115</v>
       </c>
       <c r="B9" s="2" t="s">
@@ -1735,49 +1809,49 @@
         <v>84</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" ht="277.2" x14ac:dyDescent="0.3">
-      <c r="A10" s="2" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" ht="52.8" x14ac:dyDescent="0.3">
+      <c r="A10" s="8" t="s">
         <v>121</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>84</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>124</v>
+        <v>118</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" ht="198" x14ac:dyDescent="0.3">
-      <c r="A11" s="2" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" ht="52.8" x14ac:dyDescent="0.3">
+      <c r="A11" s="8" t="s">
         <v>127</v>
       </c>
       <c r="B11" s="2" t="s">
@@ -1787,18 +1861,44 @@
         <v>84</v>
       </c>
       <c r="D11" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" ht="66" x14ac:dyDescent="0.3">
+      <c r="A12" s="8" t="s">
+        <v>253</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="D12" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="E11" s="2" t="s">
+      <c r="E12" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="F11" s="2" t="s">
+      <c r="F12" s="2" t="s">
         <v>130</v>
       </c>
-      <c r="G11" s="2" t="s">
+      <c r="G12" s="2" t="s">
         <v>131</v>
       </c>
-      <c r="H11" s="2" t="s">
+      <c r="H12" s="2" t="s">
         <v>132</v>
       </c>
     </row>
@@ -1812,381 +1912,382 @@
   <dimension ref="A1:C34"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
+    <col min="1" max="1" width="11.5546875" style="9"/>
     <col min="2" max="2" width="18.5546875" customWidth="1"/>
     <col min="3" max="3" width="39.33203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="7" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="158.4" x14ac:dyDescent="0.3">
-      <c r="A2" s="4" t="s">
+    <row r="2" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+      <c r="A2" s="10" t="s">
         <v>134</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="B2" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="C2" s="3" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="158.4" x14ac:dyDescent="0.3">
-      <c r="A3" s="4" t="s">
+    <row r="3" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+      <c r="A3" s="10" t="s">
         <v>136</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="B3" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="C3" s="3" t="s">
         <v>137</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="132" x14ac:dyDescent="0.3">
-      <c r="A4" s="4" t="s">
+    <row r="4" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="A4" s="10" t="s">
         <v>138</v>
       </c>
-      <c r="B4" s="4" t="s">
+      <c r="B4" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="C4" s="3" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="158.4" x14ac:dyDescent="0.3">
-      <c r="A5" s="4" t="s">
+    <row r="5" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+      <c r="A5" s="10" t="s">
         <v>140</v>
       </c>
-      <c r="B5" s="4" t="s">
+      <c r="B5" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C5" s="4" t="s">
+      <c r="C5" s="3" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="132" x14ac:dyDescent="0.3">
-      <c r="A6" s="4" t="s">
+    <row r="6" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+      <c r="A6" s="10" t="s">
         <v>142</v>
       </c>
-      <c r="B6" s="4" t="s">
+      <c r="B6" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C6" s="4" t="s">
+      <c r="C6" s="3" t="s">
         <v>143</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="79.2" x14ac:dyDescent="0.3">
-      <c r="A7" s="4" t="s">
+    <row r="7" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="A7" s="10" t="s">
         <v>144</v>
       </c>
-      <c r="B7" s="4" t="s">
+      <c r="B7" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C7" s="4" t="s">
+      <c r="C7" s="3" t="s">
         <v>145</v>
       </c>
     </row>
-    <row r="8" spans="1:3" ht="79.2" x14ac:dyDescent="0.3">
-      <c r="A8" s="4" t="s">
+    <row r="8" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="A8" s="10" t="s">
         <v>146</v>
       </c>
-      <c r="B8" s="4" t="s">
+      <c r="B8" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C8" s="4" t="s">
+      <c r="C8" s="3" t="s">
         <v>147</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="184.8" x14ac:dyDescent="0.3">
-      <c r="A9" s="4" t="s">
+    <row r="9" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+      <c r="A9" s="10" t="s">
         <v>148</v>
       </c>
-      <c r="B9" s="4" t="s">
+      <c r="B9" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="C9" s="4" t="s">
+      <c r="C9" s="3" t="s">
         <v>149</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="184.8" x14ac:dyDescent="0.3">
-      <c r="A10" s="4" t="s">
+    <row r="10" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+      <c r="A10" s="10" t="s">
         <v>150</v>
       </c>
-      <c r="B10" s="4" t="s">
+      <c r="B10" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="C10" s="4" t="s">
+      <c r="C10" s="3" t="s">
         <v>151</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="105.6" x14ac:dyDescent="0.3">
-      <c r="A11" s="4" t="s">
+    <row r="11" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="A11" s="10" t="s">
         <v>152</v>
       </c>
-      <c r="B11" s="4" t="s">
+      <c r="B11" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="C11" s="4" t="s">
+      <c r="C11" s="3" t="s">
         <v>153</v>
       </c>
     </row>
-    <row r="12" spans="1:3" ht="105.6" x14ac:dyDescent="0.3">
-      <c r="A12" s="4" t="s">
+    <row r="12" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="A12" s="10" t="s">
         <v>154</v>
       </c>
-      <c r="B12" s="4" t="s">
+      <c r="B12" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="C12" s="4" t="s">
+      <c r="C12" s="3" t="s">
         <v>155</v>
       </c>
     </row>
-    <row r="13" spans="1:3" ht="92.4" x14ac:dyDescent="0.3">
-      <c r="A13" s="4" t="s">
+    <row r="13" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="A13" s="10" t="s">
         <v>156</v>
       </c>
-      <c r="B13" s="4" t="s">
+      <c r="B13" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="C13" s="4" t="s">
+      <c r="C13" s="3" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="14" spans="1:3" ht="92.4" x14ac:dyDescent="0.3">
-      <c r="A14" s="4" t="s">
+    <row r="14" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="A14" s="10" t="s">
         <v>158</v>
       </c>
-      <c r="B14" s="4" t="s">
+      <c r="B14" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="C14" s="4" t="s">
+      <c r="C14" s="3" t="s">
         <v>159</v>
       </c>
     </row>
-    <row r="15" spans="1:3" ht="132" x14ac:dyDescent="0.3">
-      <c r="A15" s="4" t="s">
+    <row r="15" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="A15" s="10" t="s">
         <v>160</v>
       </c>
-      <c r="B15" s="4" t="s">
+      <c r="B15" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="C15" s="4" t="s">
+      <c r="C15" s="3" t="s">
         <v>161</v>
       </c>
     </row>
-    <row r="16" spans="1:3" ht="118.8" x14ac:dyDescent="0.3">
-      <c r="A16" s="4" t="s">
+    <row r="16" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+      <c r="A16" s="10" t="s">
         <v>162</v>
       </c>
-      <c r="B16" s="4" t="s">
+      <c r="B16" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="C16" s="4" t="s">
+      <c r="C16" s="3" t="s">
         <v>163</v>
       </c>
     </row>
-    <row r="17" spans="1:3" ht="105.6" x14ac:dyDescent="0.3">
-      <c r="A17" s="4" t="s">
+    <row r="17" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="A17" s="10" t="s">
         <v>164</v>
       </c>
-      <c r="B17" s="4" t="s">
+      <c r="B17" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="C17" s="4" t="s">
+      <c r="C17" s="3" t="s">
         <v>165</v>
       </c>
     </row>
-    <row r="18" spans="1:3" ht="105.6" x14ac:dyDescent="0.3">
-      <c r="A18" s="4" t="s">
+    <row r="18" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="A18" s="10" t="s">
         <v>166</v>
       </c>
-      <c r="B18" s="4" t="s">
+      <c r="B18" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="C18" s="4" t="s">
+      <c r="C18" s="3" t="s">
         <v>167</v>
       </c>
     </row>
-    <row r="19" spans="1:3" ht="132" x14ac:dyDescent="0.3">
-      <c r="A19" s="4" t="s">
+    <row r="19" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="A19" s="10" t="s">
         <v>168</v>
       </c>
-      <c r="B19" s="4" t="s">
+      <c r="B19" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="C19" s="4" t="s">
+      <c r="C19" s="3" t="s">
         <v>169</v>
       </c>
     </row>
-    <row r="20" spans="1:3" ht="118.8" x14ac:dyDescent="0.3">
-      <c r="A20" s="4" t="s">
+    <row r="20" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+      <c r="A20" s="10" t="s">
         <v>170</v>
       </c>
-      <c r="B20" s="4" t="s">
+      <c r="B20" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="C20" s="4" t="s">
+      <c r="C20" s="3" t="s">
         <v>171</v>
       </c>
     </row>
-    <row r="21" spans="1:3" ht="132" x14ac:dyDescent="0.3">
-      <c r="A21" s="4" t="s">
+    <row r="21" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="A21" s="10" t="s">
         <v>172</v>
       </c>
-      <c r="B21" s="4" t="s">
+      <c r="B21" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="C21" s="4" t="s">
+      <c r="C21" s="3" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="22" spans="1:3" ht="118.8" x14ac:dyDescent="0.3">
-      <c r="A22" s="4" t="s">
+    <row r="22" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="A22" s="10" t="s">
         <v>174</v>
       </c>
-      <c r="B22" s="4" t="s">
+      <c r="B22" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="C22" s="4" t="s">
+      <c r="C22" s="3" t="s">
         <v>175</v>
       </c>
     </row>
-    <row r="23" spans="1:3" ht="171.6" x14ac:dyDescent="0.3">
-      <c r="A23" s="4" t="s">
+    <row r="23" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+      <c r="A23" s="10" t="s">
         <v>176</v>
       </c>
-      <c r="B23" s="4" t="s">
+      <c r="B23" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="C23" s="4" t="s">
+      <c r="C23" s="3" t="s">
         <v>177</v>
       </c>
     </row>
-    <row r="24" spans="1:3" ht="66" x14ac:dyDescent="0.3">
-      <c r="A24" s="4" t="s">
+    <row r="24" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="A24" s="10" t="s">
         <v>178</v>
       </c>
-      <c r="B24" s="4" t="s">
+      <c r="B24" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="C24" s="4" t="s">
+      <c r="C24" s="3" t="s">
         <v>179</v>
       </c>
     </row>
-    <row r="25" spans="1:3" ht="92.4" x14ac:dyDescent="0.3">
-      <c r="A25" s="4" t="s">
+    <row r="25" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="A25" s="10" t="s">
         <v>180</v>
       </c>
-      <c r="B25" s="4" t="s">
+      <c r="B25" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="C25" s="4" t="s">
+      <c r="C25" s="3" t="s">
         <v>181</v>
       </c>
     </row>
-    <row r="26" spans="1:3" ht="105.6" x14ac:dyDescent="0.3">
-      <c r="A26" s="4" t="s">
+    <row r="26" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="A26" s="10" t="s">
         <v>182</v>
       </c>
-      <c r="B26" s="4" t="s">
+      <c r="B26" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="C26" s="4" t="s">
+      <c r="C26" s="3" t="s">
         <v>183</v>
       </c>
     </row>
-    <row r="27" spans="1:3" ht="171.6" x14ac:dyDescent="0.3">
-      <c r="A27" s="4" t="s">
+    <row r="27" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+      <c r="A27" s="10" t="s">
         <v>184</v>
       </c>
-      <c r="B27" s="4" t="s">
+      <c r="B27" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="C27" s="4" t="s">
+      <c r="C27" s="3" t="s">
         <v>185</v>
       </c>
     </row>
-    <row r="28" spans="1:3" ht="92.4" x14ac:dyDescent="0.3">
-      <c r="A28" s="4" t="s">
+    <row r="28" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="A28" s="10" t="s">
         <v>186</v>
       </c>
-      <c r="B28" s="4" t="s">
+      <c r="B28" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="C28" s="4" t="s">
+      <c r="C28" s="3" t="s">
         <v>187</v>
       </c>
     </row>
-    <row r="29" spans="1:3" ht="158.4" x14ac:dyDescent="0.3">
-      <c r="A29" s="4" t="s">
+    <row r="29" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+      <c r="A29" s="10" t="s">
         <v>188</v>
       </c>
-      <c r="B29" s="4" t="s">
+      <c r="B29" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="C29" s="4" t="s">
+      <c r="C29" s="3" t="s">
         <v>189</v>
       </c>
     </row>
-    <row r="30" spans="1:3" ht="79.2" x14ac:dyDescent="0.3">
-      <c r="A30" s="4" t="s">
+    <row r="30" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="A30" s="10" t="s">
         <v>190</v>
       </c>
-      <c r="B30" s="4" t="s">
+      <c r="B30" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="C30" s="4" t="s">
+      <c r="C30" s="3" t="s">
         <v>191</v>
       </c>
     </row>
-    <row r="31" spans="1:3" ht="118.8" x14ac:dyDescent="0.3">
-      <c r="A31" s="4" t="s">
+    <row r="31" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="A31" s="10" t="s">
         <v>192</v>
       </c>
-      <c r="B31" s="4" t="s">
+      <c r="B31" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="C31" s="4" t="s">
+      <c r="C31" s="3" t="s">
         <v>193</v>
       </c>
     </row>
-    <row r="32" spans="1:3" ht="118.8" x14ac:dyDescent="0.3">
-      <c r="A32" s="4" t="s">
+    <row r="32" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="A32" s="10" t="s">
         <v>194</v>
       </c>
-      <c r="B32" s="4" t="s">
+      <c r="B32" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="C32" s="4" t="s">
+      <c r="C32" s="3" t="s">
         <v>195</v>
       </c>
     </row>
-    <row r="33" spans="1:3" ht="105.6" x14ac:dyDescent="0.3">
-      <c r="A33" s="4" t="s">
+    <row r="33" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="A33" s="10" t="s">
         <v>196</v>
       </c>
-      <c r="B33" s="4" t="s">
+      <c r="B33" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="C33" s="4" t="s">
+      <c r="C33" s="3" t="s">
         <v>197</v>
       </c>
     </row>
-    <row r="34" spans="1:3" ht="118.8" x14ac:dyDescent="0.3">
-      <c r="A34" s="4" t="s">
+    <row r="34" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+      <c r="A34" s="10" t="s">
         <v>198</v>
       </c>
-      <c r="B34" s="4" t="s">
+      <c r="B34" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="C34" s="4" t="s">
+      <c r="C34" s="3" t="s">
         <v>199</v>
       </c>
     </row>
@@ -2205,18 +2306,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="6" t="s">
         <v>200</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="6" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="118.8" x14ac:dyDescent="0.3">
-      <c r="A2" s="2" t="s">
+    <row r="2" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+      <c r="A2" s="8" t="s">
         <v>201</v>
       </c>
       <c r="B2" s="2" t="s">
@@ -2226,8 +2327,8 @@
         <v>203</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="145.19999999999999" x14ac:dyDescent="0.3">
-      <c r="A3" s="2" t="s">
+    <row r="3" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+      <c r="A3" s="8" t="s">
         <v>201</v>
       </c>
       <c r="B3" s="2" t="s">
@@ -2237,8 +2338,8 @@
         <v>204</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="145.19999999999999" x14ac:dyDescent="0.3">
-      <c r="A4" s="2" t="s">
+    <row r="4" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+      <c r="A4" s="8" t="s">
         <v>201</v>
       </c>
       <c r="B4" s="2" t="s">
@@ -2248,290 +2349,290 @@
         <v>205</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="132" x14ac:dyDescent="0.3">
-      <c r="A5" s="2" t="s">
+    <row r="5" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="A5" s="8" t="s">
         <v>201</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>202</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="C5" s="1" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+      <c r="A6" s="8" t="s">
         <v>206</v>
       </c>
-    </row>
-    <row r="6" spans="1:3" ht="118.8" x14ac:dyDescent="0.3">
-      <c r="A6" s="2" t="s">
+      <c r="B6" s="2" t="s">
         <v>207</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="C6" s="2" t="s">
         <v>208</v>
       </c>
-      <c r="C6" s="2" t="s">
+    </row>
+    <row r="7" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+      <c r="A7" s="8" t="s">
+        <v>206</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="C7" s="2" t="s">
         <v>209</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="145.19999999999999" x14ac:dyDescent="0.3">
-      <c r="A7" s="2" t="s">
+    <row r="8" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+      <c r="A8" s="8" t="s">
+        <v>206</v>
+      </c>
+      <c r="B8" s="2" t="s">
         <v>207</v>
       </c>
-      <c r="B7" s="2" t="s">
-        <v>208</v>
-      </c>
-      <c r="C7" s="2" t="s">
+      <c r="C8" s="2" t="s">
         <v>210</v>
       </c>
     </row>
-    <row r="8" spans="1:3" ht="118.8" x14ac:dyDescent="0.3">
-      <c r="A8" s="2" t="s">
-        <v>207</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>208</v>
-      </c>
-      <c r="C8" s="2" t="s">
+    <row r="9" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="A9" s="8" t="s">
         <v>211</v>
       </c>
-    </row>
-    <row r="9" spans="1:3" ht="105.6" x14ac:dyDescent="0.3">
-      <c r="A9" s="2" t="s">
+      <c r="B9" s="2" t="s">
         <v>212</v>
       </c>
-      <c r="B9" s="2" t="s">
+      <c r="C9" s="2" t="s">
         <v>213</v>
       </c>
-      <c r="C9" s="2" t="s">
+    </row>
+    <row r="10" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+      <c r="A10" s="8" t="s">
+        <v>211</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="C10" s="2" t="s">
         <v>214</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="105.6" x14ac:dyDescent="0.3">
-      <c r="A10" s="2" t="s">
+    <row r="11" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+      <c r="A11" s="8" t="s">
+        <v>211</v>
+      </c>
+      <c r="B11" s="2" t="s">
         <v>212</v>
       </c>
-      <c r="B10" s="2" t="s">
-        <v>213</v>
-      </c>
-      <c r="C10" s="2" t="s">
+      <c r="C11" s="2" t="s">
         <v>215</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="118.8" x14ac:dyDescent="0.3">
-      <c r="A11" s="2" t="s">
-        <v>212</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>213</v>
-      </c>
-      <c r="C11" s="2" t="s">
+    <row r="12" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+      <c r="A12" s="8" t="s">
         <v>216</v>
       </c>
-    </row>
-    <row r="12" spans="1:3" ht="118.8" x14ac:dyDescent="0.3">
-      <c r="A12" s="2" t="s">
+      <c r="B12" s="2" t="s">
         <v>217</v>
       </c>
-      <c r="B12" s="2" t="s">
+      <c r="C12" s="2" t="s">
         <v>218</v>
       </c>
-      <c r="C12" s="2" t="s">
+    </row>
+    <row r="13" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+      <c r="A13" s="8" t="s">
+        <v>216</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="C13" s="2" t="s">
         <v>219</v>
       </c>
     </row>
-    <row r="13" spans="1:3" ht="132" x14ac:dyDescent="0.3">
-      <c r="A13" s="2" t="s">
-        <v>217</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>218</v>
-      </c>
-      <c r="C13" s="2" t="s">
+    <row r="14" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+      <c r="A14" s="8" t="s">
         <v>220</v>
       </c>
-    </row>
-    <row r="14" spans="1:3" ht="118.8" x14ac:dyDescent="0.3">
-      <c r="A14" s="2" t="s">
+      <c r="B14" s="2" t="s">
         <v>221</v>
       </c>
-      <c r="B14" s="2" t="s">
+      <c r="C14" s="2" t="s">
         <v>222</v>
       </c>
-      <c r="C14" s="2" t="s">
+    </row>
+    <row r="15" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="A15" s="8" t="s">
+        <v>220</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="C15" s="2" t="s">
         <v>223</v>
       </c>
     </row>
-    <row r="15" spans="1:3" ht="79.2" x14ac:dyDescent="0.3">
-      <c r="A15" s="2" t="s">
+    <row r="16" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+      <c r="A16" s="8" t="s">
+        <v>220</v>
+      </c>
+      <c r="B16" s="2" t="s">
         <v>221</v>
       </c>
-      <c r="B15" s="2" t="s">
-        <v>222</v>
-      </c>
-      <c r="C15" s="2" t="s">
+      <c r="C16" s="2" t="s">
         <v>224</v>
       </c>
     </row>
-    <row r="16" spans="1:3" ht="105.6" x14ac:dyDescent="0.3">
-      <c r="A16" s="2" t="s">
+    <row r="17" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+      <c r="A17" s="8" t="s">
+        <v>220</v>
+      </c>
+      <c r="B17" s="2" t="s">
         <v>221</v>
       </c>
-      <c r="B16" s="2" t="s">
-        <v>222</v>
-      </c>
-      <c r="C16" s="2" t="s">
+      <c r="C17" s="2" t="s">
         <v>225</v>
       </c>
     </row>
-    <row r="17" spans="1:3" ht="118.8" x14ac:dyDescent="0.3">
-      <c r="A17" s="2" t="s">
-        <v>221</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>222</v>
-      </c>
-      <c r="C17" s="2" t="s">
+    <row r="18" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+      <c r="A18" s="8" t="s">
         <v>226</v>
       </c>
-    </row>
-    <row r="18" spans="1:3" ht="132" x14ac:dyDescent="0.3">
-      <c r="A18" s="2" t="s">
+      <c r="B18" s="2" t="s">
         <v>227</v>
       </c>
-      <c r="B18" s="2" t="s">
+      <c r="C18" s="2" t="s">
         <v>228</v>
       </c>
-      <c r="C18" s="2" t="s">
+    </row>
+    <row r="19" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+      <c r="A19" s="8" t="s">
+        <v>226</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="C19" s="2" t="s">
         <v>229</v>
       </c>
     </row>
-    <row r="19" spans="1:3" ht="118.8" x14ac:dyDescent="0.3">
-      <c r="A19" s="2" t="s">
-        <v>227</v>
-      </c>
-      <c r="B19" s="2" t="s">
-        <v>228</v>
-      </c>
-      <c r="C19" s="2" t="s">
+    <row r="20" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+      <c r="A20" s="8" t="s">
         <v>230</v>
       </c>
-    </row>
-    <row r="20" spans="1:3" ht="132" x14ac:dyDescent="0.3">
-      <c r="A20" s="2" t="s">
+      <c r="B20" s="2" t="s">
         <v>231</v>
       </c>
-      <c r="B20" s="2" t="s">
+      <c r="C20" s="2" t="s">
         <v>232</v>
       </c>
-      <c r="C20" s="2" t="s">
+    </row>
+    <row r="21" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+      <c r="A21" s="8" t="s">
+        <v>230</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="C21" s="2" t="s">
         <v>233</v>
       </c>
     </row>
-    <row r="21" spans="1:3" ht="145.19999999999999" x14ac:dyDescent="0.3">
-      <c r="A21" s="2" t="s">
+    <row r="22" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+      <c r="A22" s="8" t="s">
+        <v>230</v>
+      </c>
+      <c r="B22" s="2" t="s">
         <v>231</v>
       </c>
-      <c r="B21" s="2" t="s">
-        <v>232</v>
-      </c>
-      <c r="C21" s="2" t="s">
+      <c r="C22" s="2" t="s">
         <v>234</v>
       </c>
     </row>
-    <row r="22" spans="1:3" ht="118.8" x14ac:dyDescent="0.3">
-      <c r="A22" s="2" t="s">
-        <v>231</v>
-      </c>
-      <c r="B22" s="2" t="s">
-        <v>232</v>
-      </c>
-      <c r="C22" s="2" t="s">
+    <row r="23" spans="1:3" ht="52.8" x14ac:dyDescent="0.3">
+      <c r="A23" s="8" t="s">
         <v>235</v>
       </c>
-    </row>
-    <row r="23" spans="1:3" ht="158.4" x14ac:dyDescent="0.3">
-      <c r="A23" s="2" t="s">
+      <c r="B23" s="2" t="s">
         <v>236</v>
       </c>
-      <c r="B23" s="2" t="s">
+      <c r="C23" s="2" t="s">
         <v>237</v>
       </c>
-      <c r="C23" s="2" t="s">
+    </row>
+    <row r="24" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+      <c r="A24" s="8" t="s">
+        <v>235</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>236</v>
+      </c>
+      <c r="C24" s="2" t="s">
         <v>238</v>
       </c>
     </row>
-    <row r="24" spans="1:3" ht="105.6" x14ac:dyDescent="0.3">
-      <c r="A24" s="2" t="s">
+    <row r="25" spans="1:3" ht="52.8" x14ac:dyDescent="0.3">
+      <c r="A25" s="8" t="s">
+        <v>235</v>
+      </c>
+      <c r="B25" s="2" t="s">
         <v>236</v>
       </c>
-      <c r="B24" s="2" t="s">
-        <v>237</v>
-      </c>
-      <c r="C24" s="2" t="s">
+      <c r="C25" s="2" t="s">
         <v>239</v>
       </c>
     </row>
-    <row r="25" spans="1:3" ht="145.19999999999999" x14ac:dyDescent="0.3">
-      <c r="A25" s="2" t="s">
-        <v>236</v>
-      </c>
-      <c r="B25" s="2" t="s">
-        <v>237</v>
-      </c>
-      <c r="C25" s="2" t="s">
+    <row r="26" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+      <c r="A26" s="8" t="s">
         <v>240</v>
       </c>
-    </row>
-    <row r="26" spans="1:3" ht="145.19999999999999" x14ac:dyDescent="0.3">
-      <c r="A26" s="2" t="s">
+      <c r="B26" s="2" t="s">
         <v>241</v>
       </c>
-      <c r="B26" s="2" t="s">
+      <c r="C26" s="2" t="s">
         <v>242</v>
       </c>
-      <c r="C26" s="2" t="s">
+    </row>
+    <row r="27" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+      <c r="A27" s="8" t="s">
+        <v>240</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="C27" s="2" t="s">
         <v>243</v>
       </c>
     </row>
-    <row r="27" spans="1:3" ht="145.19999999999999" x14ac:dyDescent="0.3">
-      <c r="A27" s="2" t="s">
+    <row r="28" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+      <c r="A28" s="8" t="s">
+        <v>240</v>
+      </c>
+      <c r="B28" s="2" t="s">
         <v>241</v>
       </c>
-      <c r="B27" s="2" t="s">
-        <v>242</v>
-      </c>
-      <c r="C27" s="2" t="s">
+      <c r="C28" s="2" t="s">
         <v>244</v>
       </c>
     </row>
-    <row r="28" spans="1:3" ht="105.6" x14ac:dyDescent="0.3">
-      <c r="A28" s="2" t="s">
-        <v>241</v>
-      </c>
-      <c r="B28" s="2" t="s">
-        <v>242</v>
-      </c>
-      <c r="C28" s="2" t="s">
+    <row r="29" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+      <c r="A29" s="8" t="s">
         <v>245</v>
       </c>
-    </row>
-    <row r="29" spans="1:3" ht="118.8" x14ac:dyDescent="0.3">
-      <c r="A29" s="2" t="s">
+      <c r="B29" s="2" t="s">
         <v>246</v>
       </c>
-      <c r="B29" s="2" t="s">
+      <c r="C29" s="2" t="s">
         <v>247</v>
       </c>
-      <c r="C29" s="2" t="s">
+    </row>
+    <row r="30" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+      <c r="A30" s="8" t="s">
+        <v>245</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>246</v>
+      </c>
+      <c r="C30" s="2" t="s">
         <v>248</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3" ht="132" x14ac:dyDescent="0.3">
-      <c r="A30" s="2" t="s">
-        <v>246</v>
-      </c>
-      <c r="B30" s="2" t="s">
-        <v>247</v>
-      </c>
-      <c r="C30" s="2" t="s">
-        <v>249</v>
       </c>
     </row>
   </sheetData>
@@ -2548,13 +2649,13 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:1" ht="21.6" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="5" t="s">
+      <c r="A2" s="4" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" ht="386.4" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="5" t="s">
         <v>250</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1" ht="386.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="6" t="s">
-        <v>251</v>
       </c>
     </row>
   </sheetData>
